--- a/data_static/servicos/servicos.xlsx
+++ b/data_static/servicos/servicos.xlsx
@@ -1,60 +1,344 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c476c95a5a05174c/OD/LOFEC - TAPIOCA/RCP/Aditivo/Praia segura/APP/praia_segura/data_static/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\servicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_F25DC773A252ABDACC10487E89DF624C5BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8A2520A-CD7E-43EE-9435-57EF290F133C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8C526B-02E9-482A-A872-481F4A0391C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="13770" windowHeight="15585" xr2:uid="{3A00892B-53E2-41C5-A4EF-AE7BE47453F8}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>BANHEIRO</t>
-  </si>
-  <si>
-    <t>DELEGACIA</t>
-  </si>
-  <si>
-    <t>HOSPITAL</t>
-  </si>
-  <si>
-    <t>SALVA-VIDAS</t>
-  </si>
-  <si>
-    <t>LON</t>
-  </si>
-  <si>
-    <t>LAT</t>
-  </si>
-  <si>
-    <t>NUMERO</t>
-  </si>
-  <si>
-    <t>ENDERECO</t>
-  </si>
-  <si>
-    <t>QUIOSQUES</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
+  <si>
+    <t>NOME</t>
+  </si>
+  <si>
+    <t>BH</t>
+  </si>
+  <si>
+    <t>Banheiro 04</t>
+  </si>
+  <si>
+    <t>QS</t>
+  </si>
+  <si>
+    <t>Quiosque 01</t>
+  </si>
+  <si>
+    <t>QD</t>
+  </si>
+  <si>
+    <t>Quiosque 02</t>
+  </si>
+  <si>
+    <t>Quiosque 03</t>
+  </si>
+  <si>
+    <t>Quadras de volei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Banheiro 05 </t>
+  </si>
+  <si>
+    <t>Quadras de basquete</t>
+  </si>
+  <si>
+    <t>Quadras  de futsal</t>
+  </si>
+  <si>
+    <t>RS</t>
+  </si>
+  <si>
+    <t>Pista de Skate</t>
+  </si>
+  <si>
+    <t>Quiosque 04</t>
+  </si>
+  <si>
+    <t>Banheiro 06</t>
+  </si>
+  <si>
+    <t>Quadra de basquete</t>
+  </si>
+  <si>
+    <t>Quadra</t>
+  </si>
+  <si>
+    <t>Quiosque 05</t>
+  </si>
+  <si>
+    <t>Quiosque 06</t>
+  </si>
+  <si>
+    <t>Parquinho</t>
+  </si>
+  <si>
+    <t>Banheiro 07</t>
+  </si>
+  <si>
+    <t>Quiosque 07</t>
+  </si>
+  <si>
+    <t>Quiosque 08</t>
+  </si>
+  <si>
+    <t>Quiosque 09</t>
+  </si>
+  <si>
+    <t>AC</t>
+  </si>
+  <si>
+    <t>Academia da Cidade old school</t>
+  </si>
+  <si>
+    <t>Banheiro 08</t>
+  </si>
+  <si>
+    <t>Academia da Cidade</t>
+  </si>
+  <si>
+    <t>Quiosque 10</t>
+  </si>
+  <si>
+    <t>Quiosque 11</t>
+  </si>
+  <si>
+    <t>Banheiro 09</t>
+  </si>
+  <si>
+    <t>Quiosque 12</t>
+  </si>
+  <si>
+    <t>Quiosque 13</t>
+  </si>
+  <si>
+    <t>Banheiro 10</t>
+  </si>
+  <si>
+    <t>Quiosque 14</t>
+  </si>
+  <si>
+    <t>Quiosque 15</t>
+  </si>
+  <si>
+    <t>Quiosque 16</t>
+  </si>
+  <si>
+    <t>Quiosque 17</t>
+  </si>
+  <si>
+    <t>Banheiro 11</t>
+  </si>
+  <si>
+    <t>Quiosque 18</t>
+  </si>
+  <si>
+    <t>Quiosque 19</t>
+  </si>
+  <si>
+    <t>Quiosque 20</t>
+  </si>
+  <si>
+    <t>Quiosque 21</t>
+  </si>
+  <si>
+    <t>Quiosque 22</t>
+  </si>
+  <si>
+    <t>Banheiro 12</t>
+  </si>
+  <si>
+    <t>Quiosque 23</t>
+  </si>
+  <si>
+    <t>Quiosque 24</t>
+  </si>
+  <si>
+    <t>Quiosque 25</t>
+  </si>
+  <si>
+    <t>Quiosque 26</t>
+  </si>
+  <si>
+    <t>Banheiro 13</t>
+  </si>
+  <si>
+    <t>Quiosque 27</t>
+  </si>
+  <si>
+    <t>Quiosque 28</t>
+  </si>
+  <si>
+    <t>Quiosque 29</t>
+  </si>
+  <si>
+    <t>Quiosque 30</t>
+  </si>
+  <si>
+    <t>Quiosque 31</t>
+  </si>
+  <si>
+    <t>Quiosque 32</t>
+  </si>
+  <si>
+    <t>Banheiro 14</t>
+  </si>
+  <si>
+    <t>Quiosque 33</t>
+  </si>
+  <si>
+    <t>Quiosque 34</t>
+  </si>
+  <si>
+    <t>Quiosque 35</t>
+  </si>
+  <si>
+    <t>Quiosque 36</t>
+  </si>
+  <si>
+    <t>Quiosque 37</t>
+  </si>
+  <si>
+    <t>Banheiro 15</t>
+  </si>
+  <si>
+    <t>Quiosque 38</t>
+  </si>
+  <si>
+    <t>Quiosque 39</t>
+  </si>
+  <si>
+    <t>Quiosque 40</t>
+  </si>
+  <si>
+    <t>Banheiro 16</t>
+  </si>
+  <si>
+    <t>Quiosque 41</t>
+  </si>
+  <si>
+    <t>Quiosque 42</t>
+  </si>
+  <si>
+    <t>Quiosque 43</t>
+  </si>
+  <si>
+    <t>Quiosque 44</t>
+  </si>
+  <si>
+    <t>Quiosque 45</t>
+  </si>
+  <si>
+    <t>Banheiro 17</t>
+  </si>
+  <si>
+    <t>Quiosque 46</t>
+  </si>
+  <si>
+    <t>Quiosque 47</t>
+  </si>
+  <si>
+    <t>Quiosque 48</t>
+  </si>
+  <si>
+    <t>Banheiro 18</t>
+  </si>
+  <si>
+    <t>Quiosque 49</t>
+  </si>
+  <si>
+    <t>Quiosque 50</t>
+  </si>
+  <si>
+    <t>Quiosque 51</t>
+  </si>
+  <si>
+    <t>Quiosque 52</t>
+  </si>
+  <si>
+    <t>Banheiro 19</t>
+  </si>
+  <si>
+    <t>Quiosque 53</t>
+  </si>
+  <si>
+    <t>Quiosque 54</t>
+  </si>
+  <si>
+    <t>Quiosque 55</t>
+  </si>
+  <si>
+    <t>Banheiro 20</t>
+  </si>
+  <si>
+    <t>Quiosque 56</t>
+  </si>
+  <si>
+    <t>Quiosque 57</t>
+  </si>
+  <si>
+    <t>Quiosque 58</t>
+  </si>
+  <si>
+    <t>Banheiro 21</t>
+  </si>
+  <si>
+    <t>Quiosque 59</t>
+  </si>
+  <si>
+    <t>Quiosque 60</t>
+  </si>
+  <si>
+    <t>LATITUDE</t>
+  </si>
+  <si>
+    <t>LONGITUDE</t>
+  </si>
+  <si>
+    <t>ATRIBUTO</t>
+  </si>
+  <si>
+    <t>BI</t>
+  </si>
+  <si>
+    <t>Quadra de Areia</t>
+  </si>
+  <si>
+    <t>Quadra de futsal</t>
+  </si>
+  <si>
+    <t>Mini Rampa de Skate</t>
   </si>
 </sst>
 </file>
@@ -65,7 +349,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -110,7 +394,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -120,39 +404,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -185,9 +469,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -220,6 +521,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -281,13 +599,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -296,6 +607,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -360,68 +678,1450 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E733A63B-CFF2-4536-9C50-613E53AF36D6}">
+  <dimension ref="A1:D100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.28515625" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2">
+        <v>-8.1044440000000009</v>
+      </c>
+      <c r="D2">
+        <v>-34.886313000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3">
+        <v>-8.1059529999999995</v>
+      </c>
+      <c r="D3">
+        <v>-34.887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>-8.0905050000000003</v>
+      </c>
+      <c r="D4">
+        <v>-34.881573000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>-8.0957279999999994</v>
+      </c>
+      <c r="D5">
+        <v>-34.882939</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>-8.0981710000000007</v>
+      </c>
+      <c r="D6">
+        <v>-34.883581999999997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7">
+        <v>-8.1015859999999993</v>
+      </c>
+      <c r="D7">
+        <v>-34.885005999999997</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>-8.1047670000000007</v>
+      </c>
+      <c r="D8">
+        <v>-34.886580000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9">
+        <v>-8.1081610000000008</v>
+      </c>
+      <c r="D9">
+        <v>-34.888007999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10">
+        <v>-8.1104710000000004</v>
+      </c>
+      <c r="D10">
+        <v>-34.889173999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11">
+        <v>-8.1153320000000004</v>
+      </c>
+      <c r="D11">
+        <v>-34.891995999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12">
+        <v>-8.1187880000000003</v>
+      </c>
+      <c r="D12">
+        <v>-34.894053</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13">
+        <v>-8.1219940000000008</v>
+      </c>
+      <c r="D13">
+        <v>-34.895893000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14">
+        <v>-8.1282730000000001</v>
+      </c>
+      <c r="D14">
+        <v>-34.898107000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15">
+        <v>-8.1330500000000008</v>
+      </c>
+      <c r="D15">
+        <v>-34.900229000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16">
+        <v>-8.1354539999999993</v>
+      </c>
+      <c r="D16">
+        <v>-34.901276000000003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17">
+        <v>-8.1390069999999994</v>
+      </c>
+      <c r="D17">
+        <v>-34.902408000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18">
+        <v>-8.1422030000000003</v>
+      </c>
+      <c r="D18">
+        <v>-34.903561000000003</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>82</v>
+      </c>
+      <c r="C19">
+        <v>-8.1454599999999999</v>
+      </c>
+      <c r="D19">
+        <v>-34.905169000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20">
+        <v>-8.1479890000000008</v>
+      </c>
+      <c r="D20">
+        <v>-34.906390999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>90</v>
+      </c>
+      <c r="C21">
+        <v>-8.1524629999999991</v>
+      </c>
+      <c r="D21">
+        <v>-34.908186999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>-8.1013739999999999</v>
+      </c>
+      <c r="D22">
+        <v>-34.884909999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23">
+        <v>-8.1018290000000004</v>
+      </c>
+      <c r="D23">
+        <v>-34.885151999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>96</v>
+      </c>
+      <c r="B24" t="s">
+        <v>20</v>
+      </c>
+      <c r="C24">
+        <v>-8.1022680000000005</v>
+      </c>
+      <c r="D24">
+        <v>-34.885356999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25">
+        <v>-8.1079450000000008</v>
+      </c>
+      <c r="D25">
+        <v>-34.887942000000002</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26">
+        <v>-8.1088430000000002</v>
+      </c>
+      <c r="D26">
+        <v>-34.888359000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>5</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27">
+        <v>-8.0931990000000003</v>
+      </c>
+      <c r="D27">
+        <v>-34.882052000000002</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28">
+        <v>-8.0941080000000003</v>
+      </c>
+      <c r="D28">
+        <v>-34.882280000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29">
+        <v>-8.0956159999999997</v>
+      </c>
+      <c r="D29">
+        <v>-34.882731999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30">
+        <v>-8.0960420000000006</v>
+      </c>
+      <c r="D30">
+        <v>-34.882809999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31">
+        <v>-8.0964749999999999</v>
+      </c>
+      <c r="D31">
+        <v>-34.882925999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>5</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32">
+        <v>-8.0982789999999998</v>
+      </c>
+      <c r="D32">
+        <v>-34.883426</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33">
+        <v>-8.0992840000000008</v>
+      </c>
+      <c r="D33">
+        <v>-34.883749999999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34">
+        <v>-8.0997810000000001</v>
+      </c>
+      <c r="D34">
+        <v>-34.883983000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35">
+        <v>-8.1002600000000005</v>
+      </c>
+      <c r="D35">
+        <v>-34.884166</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>-8.1007490000000004</v>
+      </c>
+      <c r="D36">
+        <v>-34.884314000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37">
+        <v>-8.1104629999999993</v>
+      </c>
+      <c r="D37">
+        <v>-34.888958000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>-8.0913869999999992</v>
+      </c>
+      <c r="D38">
+        <v>-34.881819999999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C39">
+        <v>-8.0941349999999996</v>
+      </c>
+      <c r="D39">
+        <v>-34.882508999999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
         <v>7</v>
       </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
+      <c r="C40">
+        <v>-8.0954610000000002</v>
+      </c>
+      <c r="D40">
+        <v>-34.882860000000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>-8.0979080000000003</v>
+      </c>
+      <c r="D41">
+        <v>-34.883491999999997</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42">
+        <v>-8.0999870000000005</v>
+      </c>
+      <c r="D42">
+        <v>-34.884362000000003</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>3</v>
+      </c>
+      <c r="B43" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43">
+        <v>-8.1012299999999993</v>
+      </c>
+      <c r="D43">
+        <v>-34.885004000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44">
+        <v>-8.1023259999999997</v>
+      </c>
+      <c r="D44">
+        <v>-34.885489999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="C45">
+        <v>-8.1032480000000007</v>
+      </c>
+      <c r="D45">
+        <v>-34.885922000000001</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46">
+        <v>-8.1040050000000008</v>
+      </c>
+      <c r="D46">
+        <v>-34.886253000000004</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47">
+        <v>-8.1061720000000008</v>
+      </c>
+      <c r="D47">
+        <v>-34.887248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48">
+        <v>-8.1077759999999994</v>
+      </c>
+      <c r="D48">
+        <v>-34.887967000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49">
+        <v>-8.1089000000000002</v>
+      </c>
+      <c r="D49">
+        <v>-34.888511999999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50">
+        <v>-8.11022</v>
+      </c>
+      <c r="D50">
+        <v>-34.889090000000003</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>35</v>
+      </c>
+      <c r="C51">
+        <v>-8.1119859999999999</v>
+      </c>
+      <c r="D51">
+        <v>-34.889893999999998</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52">
+        <v>-8.1129409999999993</v>
+      </c>
+      <c r="D52">
+        <v>-34.890438000000003</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>37</v>
+      </c>
+      <c r="C53">
+        <v>-8.1137720000000009</v>
+      </c>
+      <c r="D53">
+        <v>-34.890926</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54">
+        <v>-8.1146519999999995</v>
+      </c>
+      <c r="D54">
+        <v>-34.891540999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>40</v>
+      </c>
+      <c r="C55">
+        <v>-8.1155120000000007</v>
+      </c>
+      <c r="D55">
+        <v>-34.892113000000002</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56">
+        <v>-8.1161499999999993</v>
+      </c>
+      <c r="D56">
+        <v>-34.892516000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57">
+        <v>-8.1168879999999994</v>
+      </c>
+      <c r="D57">
+        <v>-34.892918999999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58">
+        <v>-8.117578</v>
+      </c>
+      <c r="D58">
+        <v>-34.893357999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59">
+        <v>-8.1185329999999993</v>
+      </c>
+      <c r="D59">
+        <v>-34.893920999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60">
+        <v>-8.1193829999999991</v>
+      </c>
+      <c r="D60">
+        <v>-34.894427999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61">
+        <v>-8.1201509999999999</v>
+      </c>
+      <c r="D61">
+        <v>-34.894885000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>48</v>
+      </c>
+      <c r="C62">
+        <v>-8.1205949999999998</v>
+      </c>
+      <c r="D62">
+        <v>-34.895135000000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>49</v>
+      </c>
+      <c r="C63">
+        <v>-8.1218610000000009</v>
+      </c>
+      <c r="D63">
+        <v>-34.895781999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>51</v>
+      </c>
+      <c r="C64">
+        <v>-8.1223899999999993</v>
+      </c>
+      <c r="D64">
+        <v>-34.896067000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>52</v>
+      </c>
+      <c r="C65">
+        <v>-8.1232729999999993</v>
+      </c>
+      <c r="D65">
+        <v>-34.896424000000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66">
+        <v>-8.1235900000000001</v>
+      </c>
+      <c r="D66">
+        <v>-34.896509999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67">
+        <v>-8.1249950000000002</v>
+      </c>
+      <c r="D67">
+        <v>-34.896937000000001</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>55</v>
+      </c>
+      <c r="C68">
+        <v>-8.1256570000000004</v>
+      </c>
+      <c r="D68">
+        <v>-34.897199999999998</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>56</v>
+      </c>
+      <c r="C69">
+        <v>-8.1268860000000007</v>
+      </c>
+      <c r="D69">
+        <v>-34.897669</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>58</v>
+      </c>
+      <c r="C70">
+        <v>-8.1284170000000007</v>
+      </c>
+      <c r="D70">
+        <v>-34.898173</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>59</v>
+      </c>
+      <c r="C71">
+        <v>-8.1296250000000008</v>
+      </c>
+      <c r="D71">
+        <v>-34.898716999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s">
+        <v>60</v>
+      </c>
+      <c r="C72">
+        <v>-8.1303070000000002</v>
+      </c>
+      <c r="D72">
+        <v>-34.899028000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>3</v>
+      </c>
+      <c r="B73" t="s">
+        <v>61</v>
+      </c>
+      <c r="C73">
+        <v>-8.1316930000000003</v>
+      </c>
+      <c r="D73">
+        <v>-34.899655000000003</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s">
+        <v>62</v>
+      </c>
+      <c r="C74">
+        <v>-8.1328870000000002</v>
+      </c>
+      <c r="D74">
+        <v>-34.900151999999999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" t="s">
+        <v>64</v>
+      </c>
+      <c r="C75">
+        <v>-8.1336980000000008</v>
+      </c>
+      <c r="D75">
+        <v>-34.900537</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s">
+        <v>65</v>
+      </c>
+      <c r="C76">
+        <v>-8.1342049999999997</v>
+      </c>
+      <c r="D76">
+        <v>-34.900775000000003</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77">
+        <v>-8.1352499999999992</v>
+      </c>
+      <c r="D77">
+        <v>-34.901195000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78">
+        <v>-8.1356929999999998</v>
+      </c>
+      <c r="D78">
+        <v>-34.901342999999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B79" t="s">
+        <v>69</v>
+      </c>
+      <c r="C79">
+        <v>-8.1370120000000004</v>
+      </c>
+      <c r="D79">
+        <v>-34.901767</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>3</v>
+      </c>
+      <c r="B80" t="s">
+        <v>70</v>
+      </c>
+      <c r="C80">
+        <v>-8.1375700000000002</v>
+      </c>
+      <c r="D80">
+        <v>-34.901938000000001</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>3</v>
+      </c>
+      <c r="B81" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81">
+        <v>-8.1381750000000004</v>
+      </c>
+      <c r="D81">
+        <v>-34.902133999999997</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>3</v>
+      </c>
+      <c r="B82" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82">
+        <v>-8.1388560000000005</v>
+      </c>
+      <c r="D82">
+        <v>-34.902355</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>3</v>
+      </c>
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83">
+        <v>-8.1392439999999997</v>
+      </c>
+      <c r="D83">
+        <v>-34.902506000000002</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>3</v>
+      </c>
+      <c r="B84" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84">
+        <v>-8.1403470000000002</v>
+      </c>
+      <c r="D84">
+        <v>-34.902827000000002</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>3</v>
+      </c>
+      <c r="B85" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85">
+        <v>-8.1409610000000008</v>
+      </c>
+      <c r="D85">
+        <v>-34.903083000000002</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>3</v>
+      </c>
+      <c r="B86" t="s">
+        <v>78</v>
+      </c>
+      <c r="C86">
+        <v>-8.1425000000000001</v>
+      </c>
+      <c r="D86">
+        <v>-34.903675999999997</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>3</v>
+      </c>
+      <c r="B87" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87">
+        <v>-8.1434449999999998</v>
+      </c>
+      <c r="D87">
+        <v>-34.904187999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>3</v>
+      </c>
+      <c r="B88" t="s">
+        <v>80</v>
+      </c>
+      <c r="C88">
+        <v>-8.1443899999999996</v>
+      </c>
+      <c r="D88">
+        <v>-34.904667000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>3</v>
+      </c>
+      <c r="B89" t="s">
+        <v>81</v>
+      </c>
+      <c r="C89">
+        <v>-8.1450510000000005</v>
+      </c>
+      <c r="D89">
+        <v>-34.905003999999998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" t="s">
+        <v>83</v>
+      </c>
+      <c r="C90">
+        <v>-8.1459360000000007</v>
+      </c>
+      <c r="D90">
+        <v>-34.905399000000003</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C91">
+        <v>-8.1465840000000007</v>
+      </c>
+      <c r="D91">
+        <v>-34.905762000000003</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" t="s">
+        <v>85</v>
+      </c>
+      <c r="C92">
+        <v>-8.1477489999999992</v>
+      </c>
+      <c r="D92">
+        <v>-34.906227999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" t="s">
+        <v>87</v>
+      </c>
+      <c r="C93">
+        <v>-8.1487370000000006</v>
+      </c>
+      <c r="D93">
+        <v>-34.906703</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94">
+        <v>-8.1495049999999996</v>
+      </c>
+      <c r="D94">
+        <v>-34.907020000000003</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" t="s">
+        <v>89</v>
+      </c>
+      <c r="C95">
+        <v>-8.1502920000000003</v>
+      </c>
+      <c r="D95">
+        <v>-34.907317999999997</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" t="s">
+        <v>91</v>
+      </c>
+      <c r="C96">
+        <v>-8.1527790000000007</v>
+      </c>
+      <c r="D96">
+        <v>-34.908312000000002</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97">
+        <v>-8.153435</v>
+      </c>
+      <c r="D97">
+        <v>-34.908586999999997</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98">
+        <v>-8.0978589999999997</v>
+      </c>
+      <c r="D98">
+        <v>-34.883291</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>12</v>
+      </c>
+      <c r="B99" t="s">
+        <v>99</v>
+      </c>
+      <c r="C99">
+        <v>-8.1030390000000008</v>
+      </c>
+      <c r="D99">
+        <v>-34.885708999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>12</v>
+      </c>
+      <c r="B100" t="s">
+        <v>99</v>
+      </c>
+      <c r="C100">
+        <v>-8.1067309999999999</v>
+      </c>
+      <c r="D100">
+        <v>-34.887467999999998</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D101">
+    <sortCondition ref="A2:A101"/>
+  </sortState>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/data_static/servicos/servicos.xlsx
+++ b/data_static/servicos/servicos.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\praia_segura_backend\data_static\servicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7DF1CE-2FBF-48A3-9327-52DB2496EA4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{865047FC-A613-4BFE-9791-CFD05B4AA292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="3540" windowWidth="21600" windowHeight="11295" xr2:uid="{3A00892B-53E2-41C5-A4EF-AE7BE47453F8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3A00892B-53E2-41C5-A4EF-AE7BE47453F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$H$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="324">
   <si>
     <t>BH</t>
   </si>
@@ -710,31 +713,317 @@
     <t>RA</t>
   </si>
   <si>
-    <t>rampa-acesso-ficticia</t>
-  </si>
-  <si>
-    <t>Rampa de acesso ficticia</t>
-  </si>
-  <si>
     <t>ES</t>
   </si>
   <si>
-    <t>Escada de acesso fictícia</t>
-  </si>
-  <si>
-    <t>escada-acesso-ficticia</t>
-  </si>
-  <si>
-    <t>Posto de Salva-vidas ficticio</t>
-  </si>
-  <si>
-    <t>sala-vidas-ficticio</t>
+    <t>banheiro-01</t>
+  </si>
+  <si>
+    <t>banheiro-02</t>
+  </si>
+  <si>
+    <t>Banheiro 01</t>
+  </si>
+  <si>
+    <t>Banheiro 02</t>
+  </si>
+  <si>
+    <t>academia-da-cidade-03</t>
+  </si>
+  <si>
+    <t>quiosque-bt-01</t>
+  </si>
+  <si>
+    <t>Quiosque 01 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quadra-01-bt</t>
+  </si>
+  <si>
+    <t>Academia da Cidade - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quiosque-bt-02</t>
+  </si>
+  <si>
+    <t>Quiosque 02 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>parquinho-bt-01</t>
+  </si>
+  <si>
+    <t>quiosque-bt-03</t>
+  </si>
+  <si>
+    <t>Quiosque 03 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quiosque-bt-04</t>
+  </si>
+  <si>
+    <t>Quiosque 04 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quiosque-bt-05</t>
+  </si>
+  <si>
+    <t>Quiosque 05 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quiosque-bt-06</t>
+  </si>
+  <si>
+    <t>Quiosque 06 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quiosque-bt-07</t>
+  </si>
+  <si>
+    <t>Quiosque 07 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>parquinho-bt-02</t>
+  </si>
+  <si>
+    <t>quiosque-bt-08</t>
+  </si>
+  <si>
+    <t>Quiosque 08 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>Quiosque 09 - Brasília Teimosa</t>
+  </si>
+  <si>
+    <t>quiosque-bt-09</t>
+  </si>
+  <si>
+    <t>quadra-02-bt</t>
+  </si>
+  <si>
+    <t>salva-vidas-01</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 01</t>
+  </si>
+  <si>
+    <t>salva-vidas-03</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 03</t>
+  </si>
+  <si>
+    <t>salva-vidas-04</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 04</t>
+  </si>
+  <si>
+    <t>salva-vidas-05</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 05</t>
+  </si>
+  <si>
+    <t>salva-vidas-06</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 06</t>
+  </si>
+  <si>
+    <t>salva-vidas-07</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 07</t>
+  </si>
+  <si>
+    <t>salva-vidas-08</t>
+  </si>
+  <si>
+    <t>Posto de Salva-vidas 08</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 08</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 09</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Escada de acesso 23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rampa de acesso 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rampa de acesso 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rampa de acesso 03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rampa de acesso 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rampa de acesso 05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rampa de acesso 06</t>
+  </si>
+  <si>
+    <t>escada-acesso-02</t>
+  </si>
+  <si>
+    <t>escada-acesso-01</t>
+  </si>
+  <si>
+    <t>escada-acesso-03</t>
+  </si>
+  <si>
+    <t>escada-acesso-04</t>
+  </si>
+  <si>
+    <t>escada-acesso-05</t>
+  </si>
+  <si>
+    <t>escada-acesso-06</t>
+  </si>
+  <si>
+    <t>escada-acesso-07</t>
+  </si>
+  <si>
+    <t>escada-acesso-08</t>
+  </si>
+  <si>
+    <t>escada-acesso-09</t>
+  </si>
+  <si>
+    <t>escada-acesso-10</t>
+  </si>
+  <si>
+    <t>escada-acesso-11</t>
+  </si>
+  <si>
+    <t>escada-acesso-12</t>
+  </si>
+  <si>
+    <t>escada-acesso-13</t>
+  </si>
+  <si>
+    <t>escada-acesso-14</t>
+  </si>
+  <si>
+    <t>escada-acesso-15</t>
+  </si>
+  <si>
+    <t>escada-acesso-16</t>
+  </si>
+  <si>
+    <t>escada-acesso-17</t>
+  </si>
+  <si>
+    <t>escada-acesso-18</t>
+  </si>
+  <si>
+    <t>escada-acesso-19</t>
+  </si>
+  <si>
+    <t>escada-acesso-20</t>
+  </si>
+  <si>
+    <t>escada-acesso-21</t>
+  </si>
+  <si>
+    <t>escada-acesso-22</t>
+  </si>
+  <si>
+    <t>escada-acesso-23</t>
+  </si>
+  <si>
+    <t>rampa-acesso-01</t>
+  </si>
+  <si>
+    <t>rampa-acesso-02</t>
+  </si>
+  <si>
+    <t>rampa-acesso-03</t>
+  </si>
+  <si>
+    <t>rampa-acesso-04</t>
+  </si>
+  <si>
+    <t>rampa-acesso-05</t>
+  </si>
+  <si>
+    <t>rampa-acesso-06</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="170" formatCode="0.000000000"/>
+    <numFmt numFmtId="171" formatCode="0.0000000000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -782,10 +1071,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1120,14 +1411,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E733A63B-CFF2-4536-9C50-613E53AF36D6}">
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H156"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="9.140625" style="1" customWidth="1"/>
     <col min="3" max="6" width="32.42578125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -1150,10 +1441,10 @@
       <c r="F1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>97</v>
       </c>
     </row>
@@ -1165,13 +1456,13 @@
         <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="1">
-        <v>-8.1044440000000009</v>
-      </c>
-      <c r="H2" s="1">
-        <v>-34.886313000000001</v>
+        <v>232</v>
+      </c>
+      <c r="G2" s="4">
+        <v>-8.081277</v>
+      </c>
+      <c r="H2" s="3">
+        <v>-34.876961000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -1184,373 +1475,373 @@
       <c r="C3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="1">
-        <v>-8.1059529999999995</v>
-      </c>
-      <c r="H3" s="1">
-        <v>-34.887</v>
+      <c r="G3" s="4">
+        <v>-8.1044440000000009</v>
+      </c>
+      <c r="H3" s="3">
+        <v>-34.886313000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="1">
-        <v>-8.0905050000000003</v>
-      </c>
-      <c r="H4" s="1">
-        <v>-34.881573000000003</v>
+        <v>22</v>
+      </c>
+      <c r="G4" s="4">
+        <v>-8.1059529999999995</v>
+      </c>
+      <c r="H4" s="3">
+        <v>-34.887</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="G5" s="1">
-        <v>-8.0957279999999994</v>
-      </c>
-      <c r="H5" s="1">
-        <v>-34.882939</v>
+        <v>226</v>
+      </c>
+      <c r="G5" s="4">
+        <v>-8.0784520000000004</v>
+      </c>
+      <c r="H5" s="3">
+        <v>-34.875998000000003</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>99</v>
+        <v>225</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="1">
-        <v>-8.0981710000000007</v>
-      </c>
-      <c r="H6" s="1">
-        <v>-34.883581999999997</v>
+        <v>227</v>
+      </c>
+      <c r="G6" s="4">
+        <v>-8.0809689999999996</v>
+      </c>
+      <c r="H6" s="3">
+        <v>-34.876685999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="1">
-        <v>-8.1015859999999993</v>
-      </c>
-      <c r="H7" s="1">
-        <v>-34.885005999999997</v>
+        <v>1</v>
+      </c>
+      <c r="G7" s="4">
+        <v>-8.0905050000000003</v>
+      </c>
+      <c r="H7" s="3">
+        <v>-34.881573000000003</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="1">
-        <v>-8.1047670000000007</v>
-      </c>
-      <c r="H8" s="1">
-        <v>-34.886580000000002</v>
+        <v>177</v>
+      </c>
+      <c r="G8" s="4">
+        <v>-8.0957279999999994</v>
+      </c>
+      <c r="H8" s="3">
+        <v>-34.882939</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="1">
-        <v>-8.1081610000000008</v>
-      </c>
-      <c r="H9" s="1">
-        <v>-34.888007999999999</v>
+        <v>10</v>
+      </c>
+      <c r="G9" s="4">
+        <v>-8.0981710000000007</v>
+      </c>
+      <c r="H9" s="3">
+        <v>-34.883581999999997</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="1">
-        <v>-8.1104710000000004</v>
-      </c>
-      <c r="H10" s="1">
-        <v>-34.889173999999997</v>
+        <v>16</v>
+      </c>
+      <c r="G10" s="4">
+        <v>-8.1015859999999993</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-34.885005999999997</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G11" s="1">
-        <v>-8.1153320000000004</v>
-      </c>
-      <c r="H11" s="1">
-        <v>-34.891995999999999</v>
+        <v>21</v>
+      </c>
+      <c r="G11" s="4">
+        <v>-8.1047670000000007</v>
+      </c>
+      <c r="H11" s="3">
+        <v>-34.886580000000002</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="1">
-        <v>-8.1187880000000003</v>
-      </c>
-      <c r="H12" s="1">
-        <v>-34.894053</v>
+        <v>25</v>
+      </c>
+      <c r="G12" s="4">
+        <v>-8.1081610000000008</v>
+      </c>
+      <c r="H12" s="3">
+        <v>-34.888007999999999</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" s="1">
-        <v>-8.1219940000000008</v>
-      </c>
-      <c r="H13" s="1">
-        <v>-34.895893000000001</v>
+        <v>28</v>
+      </c>
+      <c r="G13" s="4">
+        <v>-8.1104710000000004</v>
+      </c>
+      <c r="H13" s="3">
+        <v>-34.889173999999997</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="1">
-        <v>-8.1282730000000001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>-34.898107000000003</v>
+        <v>33</v>
+      </c>
+      <c r="G14" s="4">
+        <v>-8.1153320000000004</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-34.891995999999999</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15" s="1">
-        <v>-8.1330500000000008</v>
-      </c>
-      <c r="H15" s="1">
-        <v>-34.900229000000003</v>
+        <v>39</v>
+      </c>
+      <c r="G15" s="4">
+        <v>-8.1187880000000003</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-34.894053</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16" s="1">
-        <v>-8.1354539999999993</v>
-      </c>
-      <c r="H16" s="1">
-        <v>-34.901276000000003</v>
+        <v>44</v>
+      </c>
+      <c r="G16" s="4">
+        <v>-8.1219940000000008</v>
+      </c>
+      <c r="H16" s="3">
+        <v>-34.895893000000001</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="1">
-        <v>-8.1390069999999994</v>
-      </c>
-      <c r="H17" s="1">
-        <v>-34.902408000000001</v>
+        <v>51</v>
+      </c>
+      <c r="G17" s="4">
+        <v>-8.1282730000000001</v>
+      </c>
+      <c r="H17" s="3">
+        <v>-34.898107000000003</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G18" s="1">
-        <v>-8.1422030000000003</v>
-      </c>
-      <c r="H18" s="1">
-        <v>-34.903561000000003</v>
+        <v>57</v>
+      </c>
+      <c r="G18" s="4">
+        <v>-8.1330500000000008</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-34.900229000000003</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="1">
-        <v>-8.1454599999999999</v>
-      </c>
-      <c r="H19" s="1">
-        <v>-34.905169000000001</v>
+        <v>61</v>
+      </c>
+      <c r="G19" s="4">
+        <v>-8.1354539999999993</v>
+      </c>
+      <c r="H19" s="3">
+        <v>-34.901276000000003</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="1">
-        <v>-8.1479890000000008</v>
-      </c>
-      <c r="H20" s="1">
-        <v>-34.906390999999999</v>
+        <v>67</v>
+      </c>
+      <c r="G20" s="4">
+        <v>-8.1390069999999994</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-34.902408000000001</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="G21" s="1">
-        <v>-8.1524629999999991</v>
-      </c>
-      <c r="H21" s="1">
-        <v>-34.908186999999998</v>
+        <v>71</v>
+      </c>
+      <c r="G21" s="4">
+        <v>-8.1422030000000003</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-34.903561000000003</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>179</v>
+        <v>112</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G22" s="1">
-        <v>-8.1013739999999999</v>
-      </c>
-      <c r="H22" s="1">
-        <v>-34.884909999999998</v>
+        <v>76</v>
+      </c>
+      <c r="G22" s="4">
+        <v>-8.1454599999999999</v>
+      </c>
+      <c r="H22" s="3">
+        <v>-34.905169000000001</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G23" s="1">
-        <v>-8.1018290000000004</v>
-      </c>
-      <c r="H23" s="1">
-        <v>-34.885151999999998</v>
+        <v>80</v>
+      </c>
+      <c r="G23" s="4">
+        <v>-8.1479890000000008</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-34.906390999999999</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>180</v>
+        <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="G24" s="1">
-        <v>-8.1022680000000005</v>
-      </c>
-      <c r="H24" s="1">
-        <v>-34.885356999999999</v>
+        <v>84</v>
+      </c>
+      <c r="G24" s="4">
+        <v>-8.1524629999999991</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-34.908186999999998</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>87</v>
@@ -1558,16 +1849,16 @@
       <c r="C25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="1">
-        <v>-8.1079450000000008</v>
-      </c>
-      <c r="H25" s="1">
-        <v>-34.887942000000002</v>
+      <c r="G25" s="4">
+        <v>-8.1013739999999999</v>
+      </c>
+      <c r="H25" s="3">
+        <v>-34.884909999999998</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>87</v>
@@ -1575,1431 +1866,2270 @@
       <c r="C26" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="1">
-        <v>-8.1088430000000002</v>
-      </c>
-      <c r="H26" s="1">
-        <v>-34.888359000000001</v>
+      <c r="G26" s="4">
+        <v>-8.1018290000000004</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-34.885151999999998</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G27" s="1">
-        <v>-8.0931990000000003</v>
-      </c>
-      <c r="H27" s="1">
-        <v>-34.882052000000002</v>
+        <v>15</v>
+      </c>
+      <c r="G27" s="4">
+        <v>-8.1022680000000005</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-34.885356999999999</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G28" s="1">
-        <v>-8.0941080000000003</v>
-      </c>
-      <c r="H28" s="1">
-        <v>-34.882280000000002</v>
+        <v>15</v>
+      </c>
+      <c r="G28" s="4">
+        <v>-8.1079450000000008</v>
+      </c>
+      <c r="H28" s="3">
+        <v>-34.887942000000002</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="G29" s="1">
-        <v>-8.0956159999999997</v>
-      </c>
-      <c r="H29" s="1">
-        <v>-34.882731999999997</v>
+        <v>15</v>
+      </c>
+      <c r="G29" s="4">
+        <v>-8.1088430000000002</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-34.888359000000001</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>188</v>
+        <v>235</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G30" s="1">
-        <v>-8.0960420000000006</v>
-      </c>
-      <c r="H30" s="1">
-        <v>-34.882809999999999</v>
+        <v>15</v>
+      </c>
+      <c r="G30" s="4">
+        <v>-8.0826410000000006</v>
+      </c>
+      <c r="H30" s="3">
+        <v>-34.877378999999998</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G31" s="1">
-        <v>-8.0964749999999999</v>
-      </c>
-      <c r="H31" s="1">
-        <v>-34.882925999999998</v>
+        <v>15</v>
+      </c>
+      <c r="G31" s="4">
+        <v>-8.0855440000000005</v>
+      </c>
+      <c r="H31" s="3">
+        <v>-34.878435000000003</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>4</v>
+        <v>199</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G32" s="1">
-        <v>-8.0982789999999998</v>
-      </c>
-      <c r="H32" s="1">
-        <v>-34.883426</v>
+        <v>91</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G32" s="4">
+        <v>-8.0903150000000004</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-34.881492000000001</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>4</v>
+        <v>199</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G33" s="1">
-        <v>-8.0992840000000008</v>
-      </c>
-      <c r="H33" s="1">
-        <v>-34.883749999999999</v>
+        <v>204</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G33" s="4">
+        <v>-8.1274899999999999</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-34.901488999999998</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>192</v>
+        <v>296</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="1">
-        <v>-8.0997810000000001</v>
-      </c>
-      <c r="H34" s="1">
-        <v>-34.883983000000001</v>
+        <v>266</v>
+      </c>
+      <c r="G34" s="4">
+        <v>-8.0788601269437592</v>
+      </c>
+      <c r="H34" s="3">
+        <v>-34.875903791038297</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>193</v>
+        <v>295</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" s="1">
-        <v>-8.1002600000000005</v>
-      </c>
-      <c r="H35" s="1">
-        <v>-34.884166</v>
+        <v>267</v>
+      </c>
+      <c r="G35" s="4">
+        <v>-8.1285701620220898</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-34.898176795681202</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>194</v>
+        <v>297</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G36" s="1">
-        <v>-8.1007490000000004</v>
-      </c>
-      <c r="H36" s="1">
-        <v>-34.884314000000003</v>
+        <v>268</v>
+      </c>
+      <c r="G36" s="4">
+        <v>-8.1291637345620593</v>
+      </c>
+      <c r="H36" s="3">
+        <v>-34.898442044512898</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>195</v>
+        <v>298</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>223</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G37" s="1">
-        <v>-8.1104629999999993</v>
-      </c>
-      <c r="H37" s="1">
-        <v>-34.888958000000002</v>
+        <v>269</v>
+      </c>
+      <c r="G37" s="4">
+        <v>-8.1300714365170794</v>
+      </c>
+      <c r="H37" s="3">
+        <v>-34.8988650875337</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>115</v>
+        <v>299</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G38" s="1">
-        <v>-8.0913869999999992</v>
-      </c>
-      <c r="H38" s="1">
-        <v>-34.881819999999998</v>
+        <v>270</v>
+      </c>
+      <c r="G38" s="4">
+        <v>-8.1306492513535105</v>
+      </c>
+      <c r="H38" s="3">
+        <v>-34.8991506915362</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>116</v>
+        <v>300</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G39" s="1">
-        <v>-8.0941349999999996</v>
-      </c>
-      <c r="H39" s="1">
-        <v>-34.882508999999999</v>
+        <v>271</v>
+      </c>
+      <c r="G39" s="4">
+        <v>-8.1318128726368109</v>
+      </c>
+      <c r="H39" s="3">
+        <v>-34.899664485048902</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>301</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G40" s="1">
-        <v>-8.0954610000000002</v>
-      </c>
-      <c r="H40" s="1">
-        <v>-34.882860000000001</v>
+        <v>272</v>
+      </c>
+      <c r="G40" s="4">
+        <v>-8.13255228535707</v>
+      </c>
+      <c r="H40" s="3">
+        <v>-34.899974183259999</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>118</v>
+        <v>302</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G41" s="1">
-        <v>-8.0979080000000003</v>
-      </c>
-      <c r="H41" s="1">
-        <v>-34.883491999999997</v>
+        <v>273</v>
+      </c>
+      <c r="G41" s="4">
+        <v>-8.1333257207039793</v>
+      </c>
+      <c r="H41" s="3">
+        <v>-34.900271362927903</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>119</v>
+        <v>303</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G42" s="1">
-        <v>-8.0999870000000005</v>
-      </c>
-      <c r="H42" s="1">
-        <v>-34.884362000000003</v>
+        <v>274</v>
+      </c>
+      <c r="G42" s="4">
+        <v>-8.1341625013698895</v>
+      </c>
+      <c r="H42" s="3">
+        <v>-34.900658191350402</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>120</v>
+        <v>304</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G43" s="1">
-        <v>-8.1012299999999993</v>
-      </c>
-      <c r="H43" s="1">
-        <v>-34.885004000000002</v>
+        <v>275</v>
+      </c>
+      <c r="G43" s="4">
+        <v>-8.1348969391673691</v>
+      </c>
+      <c r="H43" s="3">
+        <v>-34.900994065757303</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>121</v>
+        <v>305</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G44" s="1">
-        <v>-8.1023259999999997</v>
-      </c>
-      <c r="H44" s="1">
-        <v>-34.885489999999997</v>
+        <v>276</v>
+      </c>
+      <c r="G44" s="4">
+        <v>-8.1365543827428901</v>
+      </c>
+      <c r="H44" s="3">
+        <v>-34.901549735421398</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>122</v>
+        <v>306</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G45" s="1">
-        <v>-8.1032480000000007</v>
-      </c>
-      <c r="H45" s="1">
-        <v>-34.885922000000001</v>
+        <v>277</v>
+      </c>
+      <c r="G45" s="4">
+        <v>-8.1372907378708508</v>
+      </c>
+      <c r="H45" s="3">
+        <v>-34.901796557577903</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>123</v>
+        <v>307</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G46" s="1">
-        <v>-8.1040050000000008</v>
-      </c>
-      <c r="H46" s="1">
-        <v>-34.886253000000004</v>
+        <v>278</v>
+      </c>
+      <c r="G46" s="4">
+        <v>-8.1386438033473301</v>
+      </c>
+      <c r="H46" s="3">
+        <v>-34.902234338981501</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>124</v>
+        <v>308</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G47" s="1">
-        <v>-8.1061720000000008</v>
-      </c>
-      <c r="H47" s="1">
-        <v>-34.887248</v>
+        <v>279</v>
+      </c>
+      <c r="G47" s="4">
+        <v>-8.1396202549121401</v>
+      </c>
+      <c r="H47" s="3">
+        <v>-34.902532278366301</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>125</v>
+        <v>309</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="1">
-        <v>-8.1077759999999994</v>
-      </c>
-      <c r="H48" s="1">
-        <v>-34.887967000000003</v>
+        <v>280</v>
+      </c>
+      <c r="G48" s="4">
+        <v>-8.1430138452531899</v>
+      </c>
+      <c r="H48" s="3">
+        <v>-34.903870640078097</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>126</v>
+        <v>310</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="1">
-        <v>-8.1089000000000002</v>
-      </c>
-      <c r="H49" s="1">
-        <v>-34.888511999999999</v>
+        <v>281</v>
+      </c>
+      <c r="G49" s="4">
+        <v>-8.1437125653417102</v>
+      </c>
+      <c r="H49" s="3">
+        <v>-34.904220872857202</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>127</v>
+        <v>311</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G50" s="1">
-        <v>-8.11022</v>
-      </c>
-      <c r="H50" s="1">
-        <v>-34.889090000000003</v>
+        <v>282</v>
+      </c>
+      <c r="G50" s="4">
+        <v>-8.1442433228756297</v>
+      </c>
+      <c r="H50" s="3">
+        <v>-34.904468032074497</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>128</v>
+        <v>312</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G51" s="1">
-        <v>-8.1119859999999999</v>
-      </c>
-      <c r="H51" s="1">
-        <v>-34.889893999999998</v>
+        <v>283</v>
+      </c>
+      <c r="G51" s="4">
+        <v>-8.1449345423420692</v>
+      </c>
+      <c r="H51" s="3">
+        <v>-34.904793557794399</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>129</v>
+        <v>313</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G52" s="1">
-        <v>-8.1129409999999993</v>
-      </c>
-      <c r="H52" s="1">
-        <v>-34.890438000000003</v>
+        <v>284</v>
+      </c>
+      <c r="G52" s="4">
+        <v>-8.1453971267522807</v>
+      </c>
+      <c r="H52" s="3">
+        <v>-34.905028912159302</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>130</v>
+        <v>314</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G53" s="1">
-        <v>-8.1137720000000009</v>
-      </c>
-      <c r="H53" s="1">
-        <v>-34.890926</v>
+        <v>285</v>
+      </c>
+      <c r="G53" s="4">
+        <v>-8.1460001199808705</v>
+      </c>
+      <c r="H53" s="3">
+        <v>-34.905309759049601</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>131</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="G54" s="1">
-        <v>-8.1146519999999995</v>
-      </c>
-      <c r="H54" s="1">
-        <v>-34.891540999999997</v>
+        <v>286</v>
+      </c>
+      <c r="G54" s="4">
+        <v>-8.1465833559825196</v>
+      </c>
+      <c r="H54" s="3">
+        <v>-34.905602864418903</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>132</v>
+        <v>316</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G55" s="1">
-        <v>-8.1155120000000007</v>
-      </c>
-      <c r="H55" s="1">
-        <v>-34.892113000000002</v>
+        <v>287</v>
+      </c>
+      <c r="G55" s="4">
+        <v>-8.1470243923496994</v>
+      </c>
+      <c r="H55" s="3">
+        <v>-34.9058023636155</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>133</v>
+        <v>317</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>2</v>
+        <v>223</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G56" s="1">
-        <v>-8.1161499999999993</v>
-      </c>
-      <c r="H56" s="1">
-        <v>-34.892516000000001</v>
+        <v>288</v>
+      </c>
+      <c r="G56" s="4">
+        <v>-8.1475138478592495</v>
+      </c>
+      <c r="H56" s="3">
+        <v>-34.906032059932201</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>134</v>
+        <v>221</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>2</v>
+        <v>213</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G57" s="1">
-        <v>-8.1168879999999994</v>
-      </c>
-      <c r="H57" s="1">
-        <v>-34.892918999999999</v>
+        <v>214</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G57" s="4">
+        <v>-8.1217100000000002</v>
+      </c>
+      <c r="H57" s="3">
+        <v>-34.895544000000001</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>135</v>
+        <v>208</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2</v>
+        <v>202</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G58" s="1">
-        <v>-8.117578</v>
-      </c>
-      <c r="H58" s="1">
-        <v>-34.893357999999999</v>
+        <v>209</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G58" s="4">
+        <v>-8.1208960000000001</v>
+      </c>
+      <c r="H58" s="3">
+        <v>-34.913857999999998</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G59" s="1">
-        <v>-8.1185329999999993</v>
-      </c>
-      <c r="H59" s="1">
-        <v>-34.893920999999999</v>
+        <v>88</v>
+      </c>
+      <c r="G59" s="4">
+        <v>-8.0931990000000003</v>
+      </c>
+      <c r="H59" s="3">
+        <v>-34.882052000000002</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>137</v>
+        <v>231</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="G60" s="1">
-        <v>-8.1193829999999991</v>
-      </c>
-      <c r="H60" s="1">
-        <v>-34.894427999999998</v>
+        <v>88</v>
+      </c>
+      <c r="G60" s="4">
+        <v>-8.0822839999999996</v>
+      </c>
+      <c r="H60" s="3">
+        <v>-34.876995000000001</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>138</v>
+        <v>186</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G61" s="1">
-        <v>-8.1201509999999999</v>
-      </c>
-      <c r="H61" s="1">
-        <v>-34.894885000000002</v>
+        <v>88</v>
+      </c>
+      <c r="G61" s="4">
+        <v>-8.0941080000000003</v>
+      </c>
+      <c r="H61" s="3">
+        <v>-34.882280000000002</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>139</v>
+        <v>251</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G62" s="1">
-        <v>-8.1205949999999998</v>
-      </c>
-      <c r="H62" s="1">
-        <v>-34.895135000000003</v>
+        <v>88</v>
+      </c>
+      <c r="G62" s="4">
+        <v>-8.0873840000000001</v>
+      </c>
+      <c r="H62" s="3">
+        <v>-34.878869999999999</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>187</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G63" s="1">
-        <v>-8.1218610000000009</v>
-      </c>
-      <c r="H63" s="1">
-        <v>-34.895781999999997</v>
+        <v>175</v>
+      </c>
+      <c r="G63" s="4">
+        <v>-8.0956159999999997</v>
+      </c>
+      <c r="H63" s="3">
+        <v>-34.882731999999997</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>141</v>
+        <v>188</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="G64" s="1">
-        <v>-8.1223899999999993</v>
-      </c>
-      <c r="H64" s="1">
-        <v>-34.896067000000002</v>
+        <v>11</v>
+      </c>
+      <c r="G64" s="4">
+        <v>-8.0960420000000006</v>
+      </c>
+      <c r="H64" s="3">
+        <v>-34.882809999999999</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G65" s="1">
-        <v>-8.1232729999999993</v>
-      </c>
-      <c r="H65" s="1">
-        <v>-34.896424000000003</v>
+        <v>89</v>
+      </c>
+      <c r="G65" s="4">
+        <v>-8.0964749999999999</v>
+      </c>
+      <c r="H65" s="3">
+        <v>-34.882925999999998</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G66" s="1">
-        <v>-8.1235900000000001</v>
-      </c>
-      <c r="H66" s="1">
-        <v>-34.896509999999999</v>
+        <v>11</v>
+      </c>
+      <c r="G66" s="4">
+        <v>-8.0982789999999998</v>
+      </c>
+      <c r="H66" s="3">
+        <v>-34.883426</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>144</v>
+        <v>191</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G67" s="1">
-        <v>-8.1249950000000002</v>
-      </c>
-      <c r="H67" s="1">
-        <v>-34.896937000000001</v>
+        <v>12</v>
+      </c>
+      <c r="G67" s="4">
+        <v>-8.0992840000000008</v>
+      </c>
+      <c r="H67" s="3">
+        <v>-34.883749999999999</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G68" s="1">
-        <v>-8.1256570000000004</v>
-      </c>
-      <c r="H68" s="1">
-        <v>-34.897199999999998</v>
+        <v>12</v>
+      </c>
+      <c r="G68" s="4">
+        <v>-8.0997810000000001</v>
+      </c>
+      <c r="H68" s="3">
+        <v>-34.883983000000001</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>146</v>
+        <v>193</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="G69" s="1">
-        <v>-8.1268860000000007</v>
-      </c>
-      <c r="H69" s="1">
-        <v>-34.897669</v>
+        <v>12</v>
+      </c>
+      <c r="G69" s="4">
+        <v>-8.1002600000000005</v>
+      </c>
+      <c r="H69" s="3">
+        <v>-34.884166</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>147</v>
+        <v>194</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G70" s="1">
-        <v>-8.1284170000000007</v>
-      </c>
-      <c r="H70" s="1">
-        <v>-34.898173</v>
+        <v>12</v>
+      </c>
+      <c r="G70" s="4">
+        <v>-8.1007490000000004</v>
+      </c>
+      <c r="H70" s="3">
+        <v>-34.884314000000003</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>148</v>
+        <v>195</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G71" s="1">
-        <v>-8.1296250000000008</v>
-      </c>
-      <c r="H71" s="1">
-        <v>-34.898716999999998</v>
+        <v>89</v>
+      </c>
+      <c r="G71" s="4">
+        <v>-8.1104629999999993</v>
+      </c>
+      <c r="H71" s="3">
+        <v>-34.888958000000002</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G72" s="1">
-        <v>-8.1303070000000002</v>
-      </c>
-      <c r="H72" s="1">
-        <v>-34.899028000000001</v>
+        <v>3</v>
+      </c>
+      <c r="G72" s="4">
+        <v>-8.0913869999999992</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-34.881819999999998</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G73" s="1">
-        <v>-8.1316930000000003</v>
-      </c>
-      <c r="H73" s="1">
-        <v>-34.899655000000003</v>
+        <v>5</v>
+      </c>
+      <c r="G73" s="4">
+        <v>-8.0941349999999996</v>
+      </c>
+      <c r="H73" s="3">
+        <v>-34.882508999999999</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G74" s="1">
-        <v>-8.1328870000000002</v>
-      </c>
-      <c r="H74" s="1">
-        <v>-34.900151999999999</v>
+        <v>6</v>
+      </c>
+      <c r="G74" s="4">
+        <v>-8.0954610000000002</v>
+      </c>
+      <c r="H74" s="3">
+        <v>-34.882860000000001</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="G75" s="1">
-        <v>-8.1336980000000008</v>
-      </c>
-      <c r="H75" s="1">
-        <v>-34.900537</v>
+        <v>9</v>
+      </c>
+      <c r="G75" s="4">
+        <v>-8.0979080000000003</v>
+      </c>
+      <c r="H75" s="3">
+        <v>-34.883491999999997</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="G76" s="1">
-        <v>-8.1342049999999997</v>
-      </c>
-      <c r="H76" s="1">
-        <v>-34.900775000000003</v>
+        <v>13</v>
+      </c>
+      <c r="G76" s="4">
+        <v>-8.0999870000000005</v>
+      </c>
+      <c r="H76" s="3">
+        <v>-34.884362000000003</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>154</v>
+        <v>120</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="G77" s="1">
-        <v>-8.1352499999999992</v>
-      </c>
-      <c r="H77" s="1">
-        <v>-34.901195000000001</v>
+        <v>14</v>
+      </c>
+      <c r="G77" s="4">
+        <v>-8.1012299999999993</v>
+      </c>
+      <c r="H77" s="3">
+        <v>-34.885004000000002</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G78" s="1">
-        <v>-8.1356929999999998</v>
-      </c>
-      <c r="H78" s="1">
-        <v>-34.901342999999997</v>
+        <v>17</v>
+      </c>
+      <c r="G78" s="4">
+        <v>-8.1023259999999997</v>
+      </c>
+      <c r="H78" s="3">
+        <v>-34.885489999999997</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G79" s="1">
-        <v>-8.1370120000000004</v>
-      </c>
-      <c r="H79" s="1">
-        <v>-34.901767</v>
+        <v>18</v>
+      </c>
+      <c r="G79" s="4">
+        <v>-8.1032480000000007</v>
+      </c>
+      <c r="H79" s="3">
+        <v>-34.885922000000001</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="G80" s="1">
-        <v>-8.1375700000000002</v>
-      </c>
-      <c r="H80" s="1">
-        <v>-34.901938000000001</v>
+        <v>19</v>
+      </c>
+      <c r="G80" s="4">
+        <v>-8.1040050000000008</v>
+      </c>
+      <c r="H80" s="3">
+        <v>-34.886253000000004</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>158</v>
+        <v>124</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G81" s="1">
-        <v>-8.1381750000000004</v>
-      </c>
-      <c r="H81" s="1">
-        <v>-34.902133999999997</v>
+        <v>23</v>
+      </c>
+      <c r="G81" s="4">
+        <v>-8.1061720000000008</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-34.887248</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G82" s="1">
-        <v>-8.1388560000000005</v>
-      </c>
-      <c r="H82" s="1">
-        <v>-34.902355</v>
+        <v>24</v>
+      </c>
+      <c r="G82" s="4">
+        <v>-8.1077759999999994</v>
+      </c>
+      <c r="H82" s="3">
+        <v>-34.887967000000003</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>160</v>
+        <v>126</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="G83" s="1">
-        <v>-8.1392439999999997</v>
-      </c>
-      <c r="H83" s="1">
-        <v>-34.902506000000002</v>
+        <v>26</v>
+      </c>
+      <c r="G83" s="4">
+        <v>-8.1089000000000002</v>
+      </c>
+      <c r="H83" s="3">
+        <v>-34.888511999999999</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G84" s="1">
-        <v>-8.1403470000000002</v>
-      </c>
-      <c r="H84" s="1">
-        <v>-34.902827000000002</v>
+        <v>27</v>
+      </c>
+      <c r="G84" s="4">
+        <v>-8.11022</v>
+      </c>
+      <c r="H84" s="3">
+        <v>-34.889090000000003</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="G85" s="1">
-        <v>-8.1409610000000008</v>
-      </c>
-      <c r="H85" s="1">
-        <v>-34.903083000000002</v>
+        <v>29</v>
+      </c>
+      <c r="G85" s="4">
+        <v>-8.1119859999999999</v>
+      </c>
+      <c r="H85" s="3">
+        <v>-34.889893999999998</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>163</v>
+        <v>129</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="G86" s="1">
-        <v>-8.1425000000000001</v>
-      </c>
-      <c r="H86" s="1">
-        <v>-34.903675999999997</v>
+        <v>30</v>
+      </c>
+      <c r="G86" s="4">
+        <v>-8.1129409999999993</v>
+      </c>
+      <c r="H86" s="3">
+        <v>-34.890438000000003</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G87" s="1">
-        <v>-8.1434449999999998</v>
-      </c>
-      <c r="H87" s="1">
-        <v>-34.904187999999998</v>
+        <v>31</v>
+      </c>
+      <c r="G87" s="4">
+        <v>-8.1137720000000009</v>
+      </c>
+      <c r="H87" s="3">
+        <v>-34.890926</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>165</v>
+        <v>131</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G88" s="1">
-        <v>-8.1443899999999996</v>
-      </c>
-      <c r="H88" s="1">
-        <v>-34.904667000000003</v>
+        <v>32</v>
+      </c>
+      <c r="G88" s="4">
+        <v>-8.1146519999999995</v>
+      </c>
+      <c r="H88" s="3">
+        <v>-34.891540999999997</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>166</v>
+        <v>132</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G89" s="1">
-        <v>-8.1450510000000005</v>
-      </c>
-      <c r="H89" s="1">
-        <v>-34.905003999999998</v>
+        <v>34</v>
+      </c>
+      <c r="G89" s="4">
+        <v>-8.1155120000000007</v>
+      </c>
+      <c r="H89" s="3">
+        <v>-34.892113000000002</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>167</v>
+        <v>133</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G90" s="1">
-        <v>-8.1459360000000007</v>
-      </c>
-      <c r="H90" s="1">
-        <v>-34.905399000000003</v>
+        <v>35</v>
+      </c>
+      <c r="G90" s="4">
+        <v>-8.1161499999999993</v>
+      </c>
+      <c r="H90" s="3">
+        <v>-34.892516000000001</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>168</v>
+        <v>134</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G91" s="1">
-        <v>-8.1465840000000007</v>
-      </c>
-      <c r="H91" s="1">
-        <v>-34.905762000000003</v>
+        <v>36</v>
+      </c>
+      <c r="G91" s="4">
+        <v>-8.1168879999999994</v>
+      </c>
+      <c r="H91" s="3">
+        <v>-34.892918999999999</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="G92" s="1">
-        <v>-8.1477489999999992</v>
-      </c>
-      <c r="H92" s="1">
-        <v>-34.906227999999999</v>
+        <v>37</v>
+      </c>
+      <c r="G92" s="4">
+        <v>-8.117578</v>
+      </c>
+      <c r="H92" s="3">
+        <v>-34.893357999999999</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>170</v>
+        <v>136</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="G93" s="1">
-        <v>-8.1487370000000006</v>
-      </c>
-      <c r="H93" s="1">
-        <v>-34.906703</v>
+        <v>38</v>
+      </c>
+      <c r="G93" s="4">
+        <v>-8.1185329999999993</v>
+      </c>
+      <c r="H93" s="3">
+        <v>-34.893920999999999</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G94" s="1">
-        <v>-8.1495049999999996</v>
-      </c>
-      <c r="H94" s="1">
-        <v>-34.907020000000003</v>
+        <v>40</v>
+      </c>
+      <c r="G94" s="4">
+        <v>-8.1193829999999991</v>
+      </c>
+      <c r="H94" s="3">
+        <v>-34.894427999999998</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="G95" s="1">
-        <v>-8.1502920000000003</v>
-      </c>
-      <c r="H95" s="1">
-        <v>-34.907317999999997</v>
+        <v>41</v>
+      </c>
+      <c r="G95" s="4">
+        <v>-8.1201509999999999</v>
+      </c>
+      <c r="H95" s="3">
+        <v>-34.894885000000002</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G96" s="1">
-        <v>-8.1527790000000007</v>
-      </c>
-      <c r="H96" s="1">
-        <v>-34.908312000000002</v>
+        <v>42</v>
+      </c>
+      <c r="G96" s="4">
+        <v>-8.1205949999999998</v>
+      </c>
+      <c r="H96" s="3">
+        <v>-34.895135000000003</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="G97" s="1">
-        <v>-8.153435</v>
-      </c>
-      <c r="H97" s="1">
-        <v>-34.908586999999997</v>
+        <v>43</v>
+      </c>
+      <c r="G97" s="4">
+        <v>-8.1218610000000009</v>
+      </c>
+      <c r="H97" s="3">
+        <v>-34.895781999999997</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G98" s="1">
-        <v>-8.0978589999999997</v>
-      </c>
-      <c r="H98" s="1">
-        <v>-34.883291</v>
+        <v>45</v>
+      </c>
+      <c r="G98" s="4">
+        <v>-8.1223899999999993</v>
+      </c>
+      <c r="H98" s="3">
+        <v>-34.896067000000002</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>197</v>
+        <v>142</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G99" s="1">
-        <v>-8.1030390000000008</v>
-      </c>
-      <c r="H99" s="1">
-        <v>-34.885708999999999</v>
+        <v>46</v>
+      </c>
+      <c r="G99" s="4">
+        <v>-8.1232729999999993</v>
+      </c>
+      <c r="H99" s="3">
+        <v>-34.896424000000003</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="G100" s="1">
-        <v>-8.1067309999999999</v>
-      </c>
-      <c r="H100" s="1">
-        <v>-34.887467999999998</v>
+        <v>47</v>
+      </c>
+      <c r="G100" s="4">
+        <v>-8.1235900000000001</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-34.896509999999999</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>206</v>
+        <v>144</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G101" s="1">
-        <v>-8.0903150000000004</v>
-      </c>
-      <c r="H101" s="1">
-        <v>-34.881492000000001</v>
+        <v>48</v>
+      </c>
+      <c r="G101" s="4">
+        <v>-8.1249950000000002</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-34.896937000000001</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>207</v>
+        <v>145</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>199</v>
+        <v>2</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G102" s="1">
-        <v>-8.1274899999999999</v>
-      </c>
-      <c r="H102" s="1">
-        <v>-34.901488999999998</v>
+        <v>49</v>
+      </c>
+      <c r="G102" s="4">
+        <v>-8.1256570000000004</v>
+      </c>
+      <c r="H102" s="3">
+        <v>-34.897199999999998</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>208</v>
+        <v>146</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>202</v>
+        <v>2</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="F103" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G103" s="1">
-        <v>-8.1208960000000001</v>
-      </c>
-      <c r="H103" s="1">
-        <v>-34.913857999999998</v>
+        <v>50</v>
+      </c>
+      <c r="G103" s="4">
+        <v>-8.1268860000000007</v>
+      </c>
+      <c r="H103" s="3">
+        <v>-34.897669</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>213</v>
+        <v>2</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="F104" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="G104" s="1">
-        <v>-8.1217100000000002</v>
-      </c>
-      <c r="H104" s="1">
-        <v>-34.895544000000001</v>
+        <v>52</v>
+      </c>
+      <c r="G104" s="4">
+        <v>-8.1284170000000007</v>
+      </c>
+      <c r="H104" s="3">
+        <v>-34.898173</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>223</v>
+        <v>148</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>222</v>
+        <v>2</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G105" s="1">
-        <v>-8.1495049999999996</v>
-      </c>
-      <c r="H105" s="1">
-        <v>-34.907020000000003</v>
+        <v>53</v>
+      </c>
+      <c r="G105" s="4">
+        <v>-8.1296250000000008</v>
+      </c>
+      <c r="H105" s="3">
+        <v>-34.898716999999998</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>225</v>
+        <v>2</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="G106" s="1">
-        <v>-8.1487370000000006</v>
-      </c>
-      <c r="H106" s="1">
-        <v>-34.906703</v>
+        <v>54</v>
+      </c>
+      <c r="G106" s="4">
+        <v>-8.1303070000000002</v>
+      </c>
+      <c r="H106" s="3">
+        <v>-34.899028000000001</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G107" s="4">
+        <v>-8.1316930000000003</v>
+      </c>
+      <c r="H107" s="3">
+        <v>-34.899655000000003</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A108" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G108" s="4">
+        <v>-8.1328870000000002</v>
+      </c>
+      <c r="H108" s="3">
+        <v>-34.900151999999999</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A109" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G109" s="4">
+        <v>-8.1336980000000008</v>
+      </c>
+      <c r="H109" s="3">
+        <v>-34.900537</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G110" s="4">
+        <v>-8.1342049999999997</v>
+      </c>
+      <c r="H110" s="3">
+        <v>-34.900775000000003</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A111" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G111" s="4">
+        <v>-8.1352499999999992</v>
+      </c>
+      <c r="H111" s="3">
+        <v>-34.901195000000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A112" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G112" s="4">
+        <v>-8.1356929999999998</v>
+      </c>
+      <c r="H112" s="3">
+        <v>-34.901342999999997</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G113" s="4">
+        <v>-8.1370120000000004</v>
+      </c>
+      <c r="H113" s="3">
+        <v>-34.901767</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A114" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G114" s="4">
+        <v>-8.1375700000000002</v>
+      </c>
+      <c r="H114" s="3">
+        <v>-34.901938000000001</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A115" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G115" s="4">
+        <v>-8.1381750000000004</v>
+      </c>
+      <c r="H115" s="3">
+        <v>-34.902133999999997</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A116" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G116" s="4">
+        <v>-8.1388560000000005</v>
+      </c>
+      <c r="H116" s="3">
+        <v>-34.902355</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A117" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G117" s="4">
+        <v>-8.1392439999999997</v>
+      </c>
+      <c r="H117" s="3">
+        <v>-34.902506000000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A118" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G118" s="4">
+        <v>-8.1403470000000002</v>
+      </c>
+      <c r="H118" s="3">
+        <v>-34.902827000000002</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A119" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G119" s="4">
+        <v>-8.1409610000000008</v>
+      </c>
+      <c r="H119" s="3">
+        <v>-34.903083000000002</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A120" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G120" s="4">
+        <v>-8.1425000000000001</v>
+      </c>
+      <c r="H120" s="3">
+        <v>-34.903675999999997</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A121" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G121" s="4">
+        <v>-8.1434449999999998</v>
+      </c>
+      <c r="H121" s="3">
+        <v>-34.904187999999998</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A122" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G122" s="4">
+        <v>-8.1443899999999996</v>
+      </c>
+      <c r="H122" s="3">
+        <v>-34.904667000000003</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G123" s="4">
+        <v>-8.1450510000000005</v>
+      </c>
+      <c r="H123" s="3">
+        <v>-34.905003999999998</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A124" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G124" s="4">
+        <v>-8.1459360000000007</v>
+      </c>
+      <c r="H124" s="3">
+        <v>-34.905399000000003</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A125" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G125" s="4">
+        <v>-8.1465840000000007</v>
+      </c>
+      <c r="H125" s="3">
+        <v>-34.905762000000003</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G126" s="4">
+        <v>-8.1477489999999992</v>
+      </c>
+      <c r="H126" s="3">
+        <v>-34.906227999999999</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A127" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G127" s="4">
+        <v>-8.1487370000000006</v>
+      </c>
+      <c r="H127" s="3">
+        <v>-34.906703</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A128" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G128" s="4">
+        <v>-8.1495049999999996</v>
+      </c>
+      <c r="H128" s="3">
+        <v>-34.907020000000003</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A129" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G129" s="4">
+        <v>-8.1502920000000003</v>
+      </c>
+      <c r="H129" s="3">
+        <v>-34.907317999999997</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A130" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G130" s="4">
+        <v>-8.1527790000000007</v>
+      </c>
+      <c r="H130" s="3">
+        <v>-34.908312000000002</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A131" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G131" s="4">
+        <v>-8.153435</v>
+      </c>
+      <c r="H131" s="3">
+        <v>-34.908586999999997</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A132" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B132" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G132" s="4">
+        <v>-8.0818060000000003</v>
+      </c>
+      <c r="H132" s="3">
+        <v>-34.877136</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A133" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G133" s="4">
+        <v>-8.0824230000000004</v>
+      </c>
+      <c r="H133" s="3">
+        <v>-34.877307000000002</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A134" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="G134" s="4">
+        <v>-8.0829210000000007</v>
+      </c>
+      <c r="H134" s="3">
+        <v>-34.877456000000002</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G135" s="4">
+        <v>-8.0831800000000005</v>
+      </c>
+      <c r="H135" s="3">
+        <v>-34.877544</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A136" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G136" s="4">
+        <v>-8.0834200000000003</v>
+      </c>
+      <c r="H136" s="3">
+        <v>-34.877642000000002</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="G137" s="4">
+        <v>-8.0835100000000004</v>
+      </c>
+      <c r="H137" s="3">
+        <v>-34.877651</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A138" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="G138" s="4">
+        <v>-8.0847789999999993</v>
+      </c>
+      <c r="H138" s="3">
+        <v>-34.878107999999997</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A139" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G139" s="4">
+        <v>-8.0860839999999996</v>
+      </c>
+      <c r="H139" s="3">
+        <v>-34.878639</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A140" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G140" s="4">
+        <v>-8.0861560000000008</v>
+      </c>
+      <c r="H140" s="3">
+        <v>-34.878658000000001</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A141" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="G141" s="4">
+        <v>-8.0936715739390603</v>
+      </c>
+      <c r="H141" s="3">
+        <v>-34.882352472951197</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A142" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="G142" s="4">
+        <v>-8.0962193078923193</v>
+      </c>
+      <c r="H142" s="3">
+        <v>-34.883028751321397</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A143" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G143" s="4">
+        <v>-8.0971851794078802</v>
+      </c>
+      <c r="H143" s="3">
+        <v>-34.883247056716598</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A144" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="G144" s="4">
+        <v>-8.0986349590912301</v>
+      </c>
+      <c r="H144" s="3">
+        <v>-34.883747734552202</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A145" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="G145" s="4">
+        <v>-8.09944096483704</v>
+      </c>
+      <c r="H145" s="3">
+        <v>-34.884138168914703</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A146" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="G146" s="4">
+        <v>-8.1006421659655992</v>
+      </c>
+      <c r="H146" s="3">
+        <v>-34.884661325153601</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A147" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G147" s="4">
+        <v>-8.0978589999999997</v>
+      </c>
+      <c r="H147" s="3">
+        <v>-34.883291</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A148" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G148" s="4">
+        <v>-8.1030390000000008</v>
+      </c>
+      <c r="H148" s="3">
+        <v>-34.885708999999999</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A149" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G149" s="4">
+        <v>-8.1067309999999999</v>
+      </c>
+      <c r="H149" s="3">
+        <v>-34.887467999999998</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A150" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B150" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G107" s="1">
-        <v>-8.1235900000000001</v>
-      </c>
-      <c r="H107" s="1">
-        <v>-34.896509999999999</v>
+      <c r="C150" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G150" s="4">
+        <v>-8.0810849999999999</v>
+      </c>
+      <c r="H150" s="3">
+        <v>-34.876716000000002</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A151" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="G151" s="4">
+        <v>-8.0994609999999998</v>
+      </c>
+      <c r="H151" s="3">
+        <v>-34.883454</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A152" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G152" s="4">
+        <v>-8.1049539999999993</v>
+      </c>
+      <c r="H152" s="3">
+        <v>-34.886229999999998</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A153" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G153" s="4">
+        <v>-8.1114119999999996</v>
+      </c>
+      <c r="H153" s="3">
+        <v>-34.889518000000002</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A154" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="G154" s="4">
+        <v>-8.1178539999999995</v>
+      </c>
+      <c r="H154" s="3">
+        <v>-34.893298999999999</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A155" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G155" s="4">
+        <v>-8.1217410000000001</v>
+      </c>
+      <c r="H155" s="3">
+        <v>-34.895539999999997</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A156" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="G156" s="4">
+        <v>-8.1510300000000004</v>
+      </c>
+      <c r="H156" s="3">
+        <v>-34.907538000000002</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:H101">
-    <sortCondition ref="B2:B101"/>
+  <autoFilter ref="A1:H1" xr:uid="{E733A63B-CFF2-4536-9C50-613E53AF36D6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H156">
+      <sortCondition ref="B1"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:H105">
+    <sortCondition ref="B4:B105"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>